--- a/Honda_Logi/Excel_Format/見積書(部単内装).xlsx
+++ b/Honda_Logi/Excel_Format/見積書(部単内装).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CE7FFF-198D-4287-AC76-CF36971BF384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED3AB69-57F2-4482-B647-5D2F527402DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{B67C730D-4A6C-492E-8EC7-2313F5669A91}"/>
   </bookViews>
@@ -151,7 +151,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +179,14 @@
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -232,12 +240,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -250,23 +261,27 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -642,11 +657,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="11.125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="17.875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="33.75" style="4" customWidth="1"/>
-    <col min="5" max="6" width="11.125" style="4" customWidth="1"/>
-    <col min="7" max="14" width="11.125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="11.125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="17.875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="33.75" style="6" customWidth="1"/>
+    <col min="5" max="7" width="11.125" style="8" customWidth="1"/>
+    <col min="8" max="14" width="11.125" style="9" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -696,54 +711,54 @@
       <c r="N3" s="3"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="E5" s="5"/>
+      <c r="E5" s="7"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="E6" s="5"/>
+      <c r="E6" s="7"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="E7" s="5"/>
+      <c r="E7" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
